--- a/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
+++ b/r5-ELGA-MOPED-main/ValueSet-moped-aufnahmeart2-valueset.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Aufnahmeart des Patienten</t>
+    <t>Aufnahmeart2 des Patienten</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://tbd.at/moped-ext-aufnahmeart</t>
+    <t>http://tbd.at/moped-ext-aufnahmeart2</t>
   </si>
 </sst>
 </file>
